--- a/data/ams_weekly_data/Nexlev/ads_report_week36.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week36.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,10 +494,10 @@
         <v>5254</v>
       </c>
       <c r="G2" t="n">
-        <v>13132.21</v>
+        <v>18216.11</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -952,35 +952,35 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev - B09GVZWJWS - Hair Comb - SP - PT</t>
+          <t>Nexlev - B0D9KFP4MG - Hair Straightener - SP - PT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>129.1</v>
+        <v>603.6600000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="F19" t="n">
-        <v>3606</v>
+        <v>9706</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3049.16</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KFP4MG - Hair Straightener - SP - PT</t>
+          <t>Nexlev - B0D9KFP4MG - Hair Straightner  - Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -989,26 +989,26 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>603.6600000000001</v>
+        <v>13.23</v>
       </c>
       <c r="E20" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>9706</v>
+        <v>332</v>
       </c>
       <c r="G20" t="n">
-        <v>3049.16</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KFP4MG - Hair Straightner  - Exact</t>
+          <t>Nexlev - B0D9KFP4MG - Hair Straightner - Exact(1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.23</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>332</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KFP4MG - Hair Straightner - Exact(1</t>
+          <t>Nexlev - B0D9KFP4MG - Hair Straightner - SP - CTR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1045,26 +1045,26 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1882.44</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
+        <v>33650</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4573.74</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KFP4MG - Hair Straightner - SP - CTR</t>
+          <t>Nexlev - B0D9KFP4MG - Hair Straightner - SP - Exact</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1073,54 +1073,54 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1882.44</v>
+        <v>1333.42</v>
       </c>
       <c r="E23" t="n">
-        <v>217</v>
+        <v>91</v>
       </c>
       <c r="F23" t="n">
-        <v>33651</v>
+        <v>16128</v>
       </c>
       <c r="G23" t="n">
-        <v>4573.74</v>
+        <v>3049.16</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KFP4MG - Hair Straightner - SP - Exact</t>
+          <t>Nexlev - B0DCGHKRXX - Hair Comb - SP - AT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1333.42</v>
+        <v>1754.71</v>
       </c>
       <c r="E24" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="F24" t="n">
-        <v>16128</v>
+        <v>114613</v>
       </c>
       <c r="G24" t="n">
-        <v>3049.16</v>
+        <v>1609.32</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Hair Comb - SP - AT</t>
+          <t>Nexlev - B0DCGHKRXX - Hair Comb - SP - PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1129,19 +1129,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1754.71</v>
+        <v>129.1</v>
       </c>
       <c r="E25" t="n">
-        <v>182</v>
+        <v>16</v>
       </c>
       <c r="F25" t="n">
-        <v>114613</v>
+        <v>3606</v>
       </c>
       <c r="G25" t="n">
-        <v>1609.32</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1583,7 +1583,7 @@
         <v>192</v>
       </c>
       <c r="F41" t="n">
-        <v>45193</v>
+        <v>45192</v>
       </c>
       <c r="G41" t="n">
         <v>5165.28</v>
@@ -1782,10 +1782,10 @@
         <v>20786</v>
       </c>
       <c r="G48" t="n">
-        <v>17786.45</v>
+        <v>20750.85</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -1863,7 +1863,7 @@
         <v>65</v>
       </c>
       <c r="F51" t="n">
-        <v>6476</v>
+        <v>6475</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1919,13 +1919,13 @@
         <v>1320</v>
       </c>
       <c r="F53" t="n">
-        <v>141427</v>
+        <v>141425</v>
       </c>
       <c r="G53" t="n">
         <v>84448.33</v>
       </c>
       <c r="H53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -1950,10 +1950,10 @@
         <v>15336</v>
       </c>
       <c r="G54" t="n">
-        <v>1694.06</v>
+        <v>3388.13</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2059,7 +2059,7 @@
         <v>174</v>
       </c>
       <c r="F58" t="n">
-        <v>37290</v>
+        <v>37286</v>
       </c>
       <c r="G58" t="n">
         <v>7149.16</v>
@@ -2143,7 +2143,7 @@
         <v>1528</v>
       </c>
       <c r="F61" t="n">
-        <v>160570</v>
+        <v>160572</v>
       </c>
       <c r="G61" t="n">
         <v>63531.42000000001</v>
@@ -2230,10 +2230,10 @@
         <v>10577</v>
       </c>
       <c r="G64" t="n">
-        <v>28036.46</v>
+        <v>30577.14</v>
       </c>
       <c r="H64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -2479,7 +2479,7 @@
         <v>234</v>
       </c>
       <c r="F73" t="n">
-        <v>39512</v>
+        <v>39511</v>
       </c>
       <c r="G73" t="n">
         <v>15246.62</v>
@@ -2566,10 +2566,10 @@
         <v>15040</v>
       </c>
       <c r="G76" t="n">
-        <v>3388.14</v>
+        <v>1694.07</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -2650,10 +2650,10 @@
         <v>33859</v>
       </c>
       <c r="G79" t="n">
-        <v>10164.42</v>
+        <v>13552.55</v>
       </c>
       <c r="H79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -2703,7 +2703,7 @@
         <v>319</v>
       </c>
       <c r="F81" t="n">
-        <v>44027</v>
+        <v>44026</v>
       </c>
       <c r="G81" t="n">
         <v>6776.26</v>
@@ -2731,7 +2731,7 @@
         <v>28</v>
       </c>
       <c r="F82" t="n">
-        <v>10290</v>
+        <v>10289</v>
       </c>
       <c r="G82" t="n">
         <v>1694.07</v>
@@ -3434,10 +3434,10 @@
         <v>5946</v>
       </c>
       <c r="G107" t="n">
-        <v>10168.64</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3465,7 +3465,7 @@
         <v>12197.45</v>
       </c>
       <c r="H108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
@@ -3518,10 +3518,10 @@
         <v>333</v>
       </c>
       <c r="G110" t="n">
-        <v>30505.94</v>
+        <v>35971.19</v>
       </c>
       <c r="H110" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -4187,7 +4187,7 @@
         <v>178</v>
       </c>
       <c r="F134" t="n">
-        <v>27956</v>
+        <v>27953</v>
       </c>
       <c r="G134" t="n">
         <v>9064.4</v>
@@ -4775,7 +4775,7 @@
         <v>135</v>
       </c>
       <c r="F155" t="n">
-        <v>13782</v>
+        <v>13781</v>
       </c>
       <c r="G155" t="n">
         <v>1355.08</v>
@@ -5279,7 +5279,7 @@
         <v>25</v>
       </c>
       <c r="F173" t="n">
-        <v>5914</v>
+        <v>5912</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>17.94</v>
+        <v>15.32</v>
       </c>
       <c r="E188" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F188" t="n">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5755,7 +5755,7 @@
         <v>34</v>
       </c>
       <c r="F190" t="n">
-        <v>4247</v>
+        <v>4244</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
         <v>3</v>
       </c>
       <c r="F193" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -6175,7 +6175,7 @@
         <v>287</v>
       </c>
       <c r="F205" t="n">
-        <v>31218</v>
+        <v>31216</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6203,7 +6203,7 @@
         <v>31</v>
       </c>
       <c r="F206" t="n">
-        <v>7677</v>
+        <v>7676</v>
       </c>
       <c r="G206" t="n">
         <v>1100.85</v>
@@ -7519,7 +7519,7 @@
         <v>13</v>
       </c>
       <c r="F253" t="n">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
         <v>5</v>
       </c>
       <c r="F258" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -8023,7 +8023,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -8051,7 +8051,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -8331,7 +8331,7 @@
         <v>3</v>
       </c>
       <c r="F282" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="F283" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G283" t="n">
         <v>0</v>
@@ -8527,7 +8527,7 @@
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -9087,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="F309" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G309" t="n">
         <v>0</v>
@@ -9227,7 +9227,7 @@
         <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         <v>8</v>
       </c>
       <c r="F316" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
         <v>10</v>
       </c>
       <c r="F320" t="n">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
         <v>152</v>
       </c>
       <c r="F335" t="n">
-        <v>12663</v>
+        <v>12662</v>
       </c>
       <c r="G335" t="n">
         <v>2964.4</v>
@@ -9871,7 +9871,7 @@
         <v>158</v>
       </c>
       <c r="F337" t="n">
-        <v>107873</v>
+        <v>107872</v>
       </c>
       <c r="G337" t="n">
         <v>5438.139999999999</v>
@@ -10011,7 +10011,7 @@
         <v>211</v>
       </c>
       <c r="F342" t="n">
-        <v>43500</v>
+        <v>43499</v>
       </c>
       <c r="G342" t="n">
         <v>3049.16</v>
@@ -10434,10 +10434,10 @@
         <v>26748</v>
       </c>
       <c r="G357" t="n">
-        <v>1863.56</v>
+        <v>3650.85</v>
       </c>
       <c r="H357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -10490,10 +10490,10 @@
         <v>9491</v>
       </c>
       <c r="G359" t="n">
-        <v>10167.8</v>
+        <v>13217.8</v>
       </c>
       <c r="H359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="360">
@@ -10599,13 +10599,13 @@
         <v>291</v>
       </c>
       <c r="F363" t="n">
-        <v>30288</v>
+        <v>30287</v>
       </c>
       <c r="G363" t="n">
-        <v>11857.63</v>
+        <v>14822.04</v>
       </c>
       <c r="H363" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364">
@@ -11579,7 +11579,7 @@
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>3394</v>
+        <v>3392</v>
       </c>
       <c r="G31" t="n">
         <v>2880.51</v>
@@ -11767,7 +11767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,23 +11826,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5837</v>
+        <v>2736</v>
       </c>
       <c r="E2" t="n">
-        <v>192</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>2759.26</v>
+        <v>1293.147205097036</v>
       </c>
       <c r="G2" t="n">
-        <v>10842.38</v>
+        <v>5081.359999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -11854,28 +11854,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- BM</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11642</v>
+        <v>3101</v>
       </c>
       <c r="E3" t="n">
-        <v>173</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>2526.56</v>
+        <v>1466.112794902964</v>
       </c>
       <c r="G3" t="n">
-        <v>13128.83</v>
+        <v>5761.02</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- Exact</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- BM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -11896,13 +11896,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8866</v>
+        <v>9013</v>
       </c>
       <c r="E4" t="n">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="F4" t="n">
-        <v>1979.89</v>
+        <v>1956.078111697691</v>
       </c>
       <c r="G4" t="n">
         <v>10164.42</v>
@@ -11920,28 +11920,28 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- BM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8457</v>
+        <v>2629</v>
       </c>
       <c r="E5" t="n">
-        <v>275</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>3072.54</v>
+        <v>570.4818883023087</v>
       </c>
       <c r="G5" t="n">
-        <v>20325.44</v>
+        <v>2964.41</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -11953,28 +11953,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7569</v>
+        <v>8866</v>
       </c>
       <c r="E6" t="n">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="F6" t="n">
-        <v>1117.34</v>
+        <v>1979.89</v>
       </c>
       <c r="G6" t="n">
-        <v>2541.52</v>
+        <v>10164.42</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -11986,28 +11986,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01-SBV</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>793</v>
+        <v>8457</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="F7" t="n">
-        <v>667.49</v>
+        <v>3072.54</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>20325.44</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -12019,28 +12019,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9226</v>
+        <v>7569</v>
       </c>
       <c r="E8" t="n">
-        <v>121</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>1098.326666666667</v>
+        <v>1117.34</v>
       </c>
       <c r="G8" t="n">
-        <v>11803.11</v>
+        <v>2541.52</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -12052,28 +12052,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01-SBV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9226</v>
+        <v>793</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
-        <v>1098.326666666667</v>
+        <v>667.49</v>
       </c>
       <c r="G9" t="n">
-        <v>11803.11</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -12090,23 +12090,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9226</v>
+        <v>5857</v>
       </c>
       <c r="E10" t="n">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="F10" t="n">
-        <v>1098.326666666667</v>
+        <v>697.2791165600028</v>
       </c>
       <c r="G10" t="n">
-        <v>11803.11</v>
+        <v>7493.273507087025</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -12118,28 +12118,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT2</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8117</v>
+        <v>2783</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>797.37</v>
+        <v>331.2854756553394</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3560.142013513551</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -12151,28 +12151,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-Spot Cleaner Machine-B0GGHZWMVW-SBV-PT2</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>675</v>
+        <v>8788</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="F12" t="n">
-        <v>90.23</v>
+        <v>1046.266476792399</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>11243.6478960963</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -12184,28 +12184,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1721</v>
+        <v>10249</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="F13" t="n">
-        <v>131.2</v>
+        <v>1220.148930992259</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>13112.26658330312</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -12217,22 +12217,22 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM2</t>
+          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>8117</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>2.99</v>
+        <v>797.37</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -12250,28 +12250,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Spot Cleaner Machine-B0GGHZWMVW-SBV-PT2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15947</v>
+        <v>675</v>
       </c>
       <c r="E15" t="n">
-        <v>871</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>6204.206666666666</v>
+        <v>90.23</v>
       </c>
       <c r="G15" t="n">
-        <v>110572.95</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -12283,28 +12283,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15947</v>
+        <v>1721</v>
       </c>
       <c r="E16" t="n">
-        <v>871</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>6204.206666666666</v>
+        <v>131.2</v>
       </c>
       <c r="G16" t="n">
-        <v>110572.95</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -12316,28 +12316,28 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15947</v>
+        <v>79</v>
       </c>
       <c r="E17" t="n">
-        <v>871</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>6204.206666666666</v>
+        <v>2.99</v>
       </c>
       <c r="G17" t="n">
-        <v>110572.95</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12358,19 +12358,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12268</v>
+        <v>14692</v>
       </c>
       <c r="E18" t="n">
-        <v>294</v>
+        <v>803</v>
       </c>
       <c r="F18" t="n">
-        <v>2726.42</v>
+        <v>5716.119810415219</v>
       </c>
       <c r="G18" t="n">
-        <v>10164.42</v>
+        <v>103694.941143565</v>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -12382,28 +12382,28 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24907</v>
+        <v>8818</v>
       </c>
       <c r="E19" t="n">
-        <v>606</v>
+        <v>482</v>
       </c>
       <c r="F19" t="n">
-        <v>5096.17</v>
+        <v>3430.778340775684</v>
       </c>
       <c r="G19" t="n">
-        <v>9657.629999999999</v>
+        <v>62237.03664768182</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -12415,28 +12415,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4384</v>
+        <v>24198</v>
       </c>
       <c r="E20" t="n">
-        <v>157</v>
+        <v>1322</v>
       </c>
       <c r="F20" t="n">
-        <v>2007.72</v>
+        <v>9414.309099016547</v>
       </c>
       <c r="G20" t="n">
-        <v>10502.54</v>
+        <v>170783.0242030803</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -12448,28 +12448,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17787</v>
+        <v>132</v>
       </c>
       <c r="E21" t="n">
-        <v>336</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>2782.35</v>
+        <v>51.41274979254828</v>
       </c>
       <c r="G21" t="n">
-        <v>12112.72</v>
+        <v>932.6680056728667</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -12481,28 +12481,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>868</v>
+        <v>12268</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>294</v>
       </c>
       <c r="F22" t="n">
-        <v>195.3</v>
+        <v>2726.42</v>
       </c>
       <c r="G22" t="n">
-        <v>11120.07</v>
+        <v>10164.42</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -12514,28 +12514,28 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7708</v>
+        <v>8738</v>
       </c>
       <c r="E23" t="n">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="F23" t="n">
-        <v>1730.37</v>
+        <v>1787.864872002759</v>
       </c>
       <c r="G23" t="n">
-        <v>10251.7</v>
+        <v>3388.14</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -12547,28 +12547,28 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9677</v>
+        <v>8303</v>
       </c>
       <c r="E24" t="n">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="F24" t="n">
-        <v>3317.54</v>
+        <v>1698.871084655345</v>
       </c>
       <c r="G24" t="n">
-        <v>21174.58</v>
+        <v>3219.489999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12589,19 +12589,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14386</v>
+        <v>7866</v>
       </c>
       <c r="E25" t="n">
-        <v>317</v>
+        <v>191</v>
       </c>
       <c r="F25" t="n">
-        <v>3850.76</v>
+        <v>1609.434043341897</v>
       </c>
       <c r="G25" t="n">
-        <v>26258.49</v>
+        <v>3050</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -12613,28 +12613,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - B0F43P6D23 - Phrase</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8664</v>
+        <v>3182</v>
       </c>
       <c r="E26" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F26" t="n">
-        <v>1530.49</v>
+        <v>1457.068685175205</v>
       </c>
       <c r="G26" t="n">
-        <v>2540.68</v>
+        <v>7622.04</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -12646,25 +12646,25 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - BM(2)</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>909</v>
+        <v>1202</v>
       </c>
       <c r="E27" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F27" t="n">
-        <v>134.85</v>
+        <v>550.6513148247949</v>
       </c>
       <c r="G27" t="n">
-        <v>2964.4</v>
+        <v>2880.5</v>
       </c>
       <c r="H27" t="n">
         <v>1</v>
@@ -12679,28 +12679,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - BM(3)</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1238</v>
+        <v>11193</v>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="F28" t="n">
-        <v>358.31</v>
+        <v>1750.819220951198</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>7622.039999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -12712,28 +12712,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - Exact</t>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1311</v>
+        <v>6594</v>
       </c>
       <c r="E29" t="n">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="F29" t="n">
-        <v>373.75</v>
+        <v>1031.530779048802</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4490.68</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -12745,28 +12745,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlex - Steam Cleaner - SB - Phrase</t>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2707</v>
+        <v>868</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>435.32</v>
+        <v>195.3</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>14000.58</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -12778,30 +12778,426 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>4332</v>
+      </c>
+      <c r="E31" t="n">
+        <v>98</v>
+      </c>
+      <c r="F31" t="n">
+        <v>972.3944494474086</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5761.02</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0GM1CZC7Y</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3376</v>
+      </c>
+      <c r="E32" t="n">
+        <v>76</v>
+      </c>
+      <c r="F32" t="n">
+        <v>757.9755505525912</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4490.68</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1548</v>
+      </c>
+      <c r="E33" t="n">
+        <v>53</v>
+      </c>
+      <c r="F33" t="n">
+        <v>530.8388631840631</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3862.474607694699</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>8129</v>
+      </c>
+      <c r="E34" t="n">
+        <v>278</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2786.701136815937</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20276.5153923053</v>
+      </c>
+      <c r="H34" t="n">
+        <v>7</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2092</v>
+      </c>
+      <c r="E35" t="n">
+        <v>46</v>
+      </c>
+      <c r="F35" t="n">
+        <v>560.0956975506223</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3819.31547880835</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3140</v>
+      </c>
+      <c r="E36" t="n">
+        <v>69</v>
+      </c>
+      <c r="F36" t="n">
+        <v>840.4229213602769</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5730.878288002788</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>9154</v>
+      </c>
+      <c r="E37" t="n">
+        <v>202</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2450.241381089101</v>
+      </c>
+      <c r="G37" t="n">
+        <v>16708.29623318886</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - B0F43P6D23 - Phrase</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>8664</v>
+      </c>
+      <c r="E38" t="n">
+        <v>118</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1530.49</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2540.68</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - BM(2)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>909</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" t="n">
+        <v>134.85</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2964.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - BM(3)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1238</v>
+      </c>
+      <c r="E40" t="n">
+        <v>43</v>
+      </c>
+      <c r="F40" t="n">
+        <v>358.31</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - Exact</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1311</v>
+      </c>
+      <c r="E41" t="n">
+        <v>27</v>
+      </c>
+      <c r="F41" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - Phrase</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2707</v>
+      </c>
+      <c r="E42" t="n">
+        <v>31</v>
+      </c>
+      <c r="F42" t="n">
+        <v>435.32</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Nexlex - Steame Cleaner - SB - Phrase</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>B0F43P6D23</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D43" t="n">
         <v>2355</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E43" t="n">
         <v>33</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F43" t="n">
         <v>396.8</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
